--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122035103</v>
+        <v>122034574</v>
       </c>
       <c r="B2" t="n">
-        <v>58079</v>
+        <v>58052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670264</v>
+        <v>670185</v>
       </c>
       <c r="R2" t="n">
-        <v>6562650</v>
+        <v>6562590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -910,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122034574</v>
+        <v>122035103</v>
       </c>
       <c r="B4" t="n">
-        <v>58052</v>
+        <v>58079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,7 +945,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670185</v>
+        <v>670264</v>
       </c>
       <c r="R4" t="n">
-        <v>6562590</v>
+        <v>6562650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +984,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034574</v>
+        <v>122034674</v>
       </c>
       <c r="B2" t="n">
-        <v>58052</v>
+        <v>57856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670185</v>
+        <v>670238</v>
       </c>
       <c r="R2" t="n">
-        <v>6562590</v>
+        <v>6562668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034674</v>
+        <v>122034574</v>
       </c>
       <c r="B3" t="n">
-        <v>57856</v>
+        <v>58052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670238</v>
+        <v>670185</v>
       </c>
       <c r="R3" t="n">
-        <v>6562668</v>
+        <v>6562590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034674</v>
+        <v>122035103</v>
       </c>
       <c r="B2" t="n">
-        <v>57856</v>
+        <v>58079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670238</v>
+        <v>670264</v>
       </c>
       <c r="R2" t="n">
-        <v>6562668</v>
+        <v>6562650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034574</v>
+        <v>122034674</v>
       </c>
       <c r="B3" t="n">
-        <v>58052</v>
+        <v>57856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +835,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670185</v>
+        <v>670238</v>
       </c>
       <c r="R3" t="n">
-        <v>6562590</v>
+        <v>6562668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122035103</v>
+        <v>122034574</v>
       </c>
       <c r="B4" t="n">
-        <v>58079</v>
+        <v>58052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +922,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +950,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670264</v>
+        <v>670185</v>
       </c>
       <c r="R4" t="n">
-        <v>6562650</v>
+        <v>6562590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,17 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122035103</v>
+        <v>122034574</v>
       </c>
       <c r="B2" t="n">
-        <v>58079</v>
+        <v>58057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670264</v>
+        <v>670185</v>
       </c>
       <c r="R2" t="n">
-        <v>6562650</v>
+        <v>6562590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034674</v>
+        <v>122035103</v>
       </c>
       <c r="B3" t="n">
-        <v>57856</v>
+        <v>58084</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670238</v>
+        <v>670264</v>
       </c>
       <c r="R3" t="n">
-        <v>6562668</v>
+        <v>6562650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,12 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122034574</v>
+        <v>122034674</v>
       </c>
       <c r="B4" t="n">
-        <v>58052</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +922,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670185</v>
+        <v>670238</v>
       </c>
       <c r="R4" t="n">
-        <v>6562590</v>
+        <v>6562668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lark Davis, Maryam Bessouda, Josefin Hagernäs</t>
+          <t>Josefin Hagernäs, Lark Davis, Maryam Bessouda</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Josefin Hagernäs, Lark Davis, Maryam Bessouda</t>
+          <t>Lark Davis, Maryam Bessouda, Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>126941524</v>
       </c>
       <c r="B5" t="n">
-        <v>56539</v>
+        <v>56543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>126941525</v>
       </c>
       <c r="B6" t="n">
-        <v>56544</v>
+        <v>56548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>126941524</v>
       </c>
       <c r="B5" t="n">
-        <v>56543</v>
+        <v>56545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>126941525</v>
       </c>
       <c r="B6" t="n">
-        <v>56548</v>
+        <v>56550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034574</v>
+        <v>126941524</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björksättra, Srm</t>
+          <t>Gladö industriområde, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670185</v>
+        <v>670205</v>
       </c>
       <c r="R2" t="n">
-        <v>6562590</v>
+        <v>6562743</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering Ekologigruppen AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,75 +786,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Lark Davis</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Josefin Hagernäs, Maryam Bessouda, Lark Davis</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+          <t>Fladdermusinventering vid Gladö industriområde, 2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122035103</v>
+        <v>119347600</v>
       </c>
       <c r="B3" t="n">
-        <v>58084</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670264</v>
+        <v>670274</v>
       </c>
       <c r="R3" t="n">
-        <v>6562650</v>
+        <v>6562635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,17 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,17 +887,17 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Jörgen Wissman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Jörgen Wissman, Jacqueline Nelms</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+          <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
     </row>
@@ -913,16 +906,11 @@
         <v>122034674</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1025,69 +1013,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126941524</v>
+        <v>122034580</v>
       </c>
       <c r="B5" t="n">
-        <v>56545</v>
+        <v>58602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gladö industriområde, Srm</t>
+          <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670205</v>
+        <v>670195</v>
       </c>
       <c r="R5" t="n">
-        <v>6562743</v>
+        <v>6562440</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,17 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fladdermusinventering Ekologigruppen AB</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,48 +1107,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lark Davis</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lark Davis, Maryam Bessouda, Josefin Hagernäs</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Fladdermusinventering vid Gladö industriområde, 2024</t>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126941525</v>
+        <v>122034581</v>
       </c>
       <c r="B6" t="n">
-        <v>56550</v>
+        <v>58602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,36 +1156,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gladö industriområde, Srm</t>
+          <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670205</v>
+        <v>670268</v>
       </c>
       <c r="R6" t="n">
-        <v>6562743</v>
+        <v>6562595</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,17 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fladdermusinventering Ekologigruppen AB</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,15 +1217,473 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122034756</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>670346</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6562802</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ser den bara</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122034574</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>670185</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6562590</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122035103</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>670264</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6562650</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>verkar ha bo i roshög tsm med sjungande gärdsmyg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126941525</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gladö industriområde, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>670205</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering Ekologigruppen AB</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Lark Davis</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lark Davis, Maryam Bessouda, Josefin Hagernäs</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Josefin Hagernäs, Maryam Bessouda, Lark Davis</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Fladdermusinventering vid Gladö industriområde, 2024</t>
         </is>

--- a/artfynd/A 52259-2024 artfynd.xlsx
+++ b/artfynd/A 52259-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
           <t>Fladdermusinventering vid Gladö industriområde, 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126941524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034574</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122035103</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,8 +1733,24 @@
           <t>Fladdermusinventering vid Gladö industriområde, 2024</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126941525</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>